--- a/data/trans_orig/P33_1_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2007</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2007 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>717319</t>
+          <t>715849</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>771320</t>
+          <t>770460</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>825141</t>
+          <t>821955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>892411</t>
+          <t>888029</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1560688</t>
+          <t>1558857</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1650592</t>
+          <t>1648372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,81%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>248008</t>
+          <t>248868</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>302009</t>
+          <t>303479</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>415978</t>
+          <t>420360</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>483248</t>
+          <t>486434</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>677125</t>
+          <t>679345</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>767029</t>
+          <t>768860</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1402161</t>
+          <t>1402471</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1458918</t>
+          <t>1460850</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1262784</t>
+          <t>1260626</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1323333</t>
+          <t>1320486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2683318</t>
+          <t>2680751</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2767718</t>
+          <t>2764951</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,37%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206425</t>
+          <t>204493</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>263182</t>
+          <t>262872</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>249940</t>
+          <t>252787</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>310489</t>
+          <t>312647</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>470899</t>
+          <t>473666</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>555299</t>
+          <t>557866</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>436532</t>
+          <t>436200</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>470745</t>
+          <t>472008</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>379756</t>
+          <t>379505</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>410821</t>
+          <t>411829</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>825707</t>
+          <t>828307</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>875693</t>
+          <t>873958</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74189</t>
+          <t>72926</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108402</t>
+          <t>108734</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64655</t>
+          <t>63647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95720</t>
+          <t>95971</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144716</t>
+          <t>146451</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194702</t>
+          <t>192102</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2588708</t>
+          <t>2582930</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2674029</t>
+          <t>2674378</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2501367</t>
+          <t>2498276</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2598566</t>
+          <t>2596209</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5118185</t>
+          <t>5112156</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5248700</t>
+          <t>5243770</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,61%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>555576</t>
+          <t>555227</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>640897</t>
+          <t>646675</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>758572</t>
+          <t>760929</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>855771</t>
+          <t>858862</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1338043</t>
+          <t>1342973</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1468558</t>
+          <t>1474587</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2012</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2012 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>604121</t>
+          <t>598836</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>663796</t>
+          <t>663580</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>717008</t>
+          <t>720591</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>791135</t>
+          <t>793971</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1338750</t>
+          <t>1342535</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1435513</t>
+          <t>1434820</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,28%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>305394</t>
+          <t>305610</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>365069</t>
+          <t>370354</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>543574</t>
+          <t>540738</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>617701</t>
+          <t>614118</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>868386</t>
+          <t>869079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>965149</t>
+          <t>961364</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1479928</t>
+          <t>1481020</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1557704</t>
+          <t>1555293</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1225551</t>
+          <t>1225393</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1303776</t>
+          <t>1302014</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2724999</t>
+          <t>2725328</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2837037</t>
+          <t>2842446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,66%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>398487</t>
+          <t>400898</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>476263</t>
+          <t>475171</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447763</t>
+          <t>449525</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>525988</t>
+          <t>526146</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>870693</t>
+          <t>865284</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>982731</t>
+          <t>982402</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>351939</t>
+          <t>350139</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>390974</t>
+          <t>389777</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>355168</t>
+          <t>353969</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>387278</t>
+          <t>390212</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>719127</t>
+          <t>719092</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>770515</t>
+          <t>770383</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,97%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90207</t>
+          <t>91404</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129242</t>
+          <t>131042</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71353</t>
+          <t>68419</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103463</t>
+          <t>104662</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>169298</t>
+          <t>169430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>220686</t>
+          <t>220721</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2470376</t>
+          <t>2474890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2577049</t>
+          <t>2581412</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2336731</t>
+          <t>2333200</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2442970</t>
+          <t>2445622</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4834427</t>
+          <t>4835130</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4998194</t>
+          <t>5000791</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,94%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>829514</t>
+          <t>825151</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>936187</t>
+          <t>931673</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1101909</t>
+          <t>1099257</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1208148</t>
+          <t>1211679</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1953248</t>
+          <t>1950651</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2117015</t>
+          <t>2116312</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2016</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2016 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>505445</t>
+          <t>503990</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>552574</t>
+          <t>552436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>556060</t>
+          <t>560160</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>619792</t>
+          <t>625834</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1079398</t>
+          <t>1078417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1163011</t>
+          <t>1157105</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,56%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199766</t>
+          <t>199904</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246895</t>
+          <t>248350</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>366315</t>
+          <t>360273</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430047</t>
+          <t>425947</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>575436</t>
+          <t>581342</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>659049</t>
+          <t>660030</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1586146</t>
+          <t>1583051</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1662305</t>
+          <t>1658541</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1445813</t>
+          <t>1450476</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1526412</t>
+          <t>1526268</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3059583</t>
+          <t>3052811</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3169142</t>
+          <t>3168567</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,16%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>409320</t>
+          <t>413084</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>485479</t>
+          <t>488574</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>455901</t>
+          <t>456045</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>536500</t>
+          <t>531837</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>884796</t>
+          <t>885371</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>994355</t>
+          <t>1001127</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>408391</t>
+          <t>412760</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>451949</t>
+          <t>453189</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>411459</t>
+          <t>411655</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>451704</t>
+          <t>450312</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>836891</t>
+          <t>836189</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>893101</t>
+          <t>888312</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,05%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94937</t>
+          <t>93697</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138495</t>
+          <t>134126</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97436</t>
+          <t>98828</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137681</t>
+          <t>137485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>202926</t>
+          <t>207715</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>259136</t>
+          <t>259838</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2538860</t>
+          <t>2535032</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2637967</t>
+          <t>2633441</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2462005</t>
+          <t>2457747</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2570547</t>
+          <t>2573138</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5029752</t>
+          <t>5023181</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5186334</t>
+          <t>5177445</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,16%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>732885</t>
+          <t>737411</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>831992</t>
+          <t>835820</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>947014</t>
+          <t>944423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1055556</t>
+          <t>1059814</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1702079</t>
+          <t>1710968</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1858661</t>
+          <t>1865232</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2023</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2023 (tasa de respuesta: 97,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>311994</t>
+          <t>313265</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>350991</t>
+          <t>350918</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>413669</t>
+          <t>411879</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>452286</t>
+          <t>450684</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>736454</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>790178</t>
+          <t>792333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,91%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>148755</t>
+          <t>148828</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>187752</t>
+          <t>186481</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268701</t>
+          <t>270303</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>307318</t>
+          <t>309108</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>430556</t>
+          <t>428401</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>484280</t>
+          <t>482781</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,55%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1680146</t>
+          <t>1679512</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1918211</t>
+          <t>1925836</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1059103</t>
+          <t>1054759</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1607844</t>
+          <t>1612874</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2746093</t>
+          <t>2687633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3401234</t>
+          <t>3398512</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,47%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>292690</t>
+          <t>285065</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>530755</t>
+          <t>531389</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>567874</t>
+          <t>562844</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1116615</t>
+          <t>1120959</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>985384</t>
+          <t>988106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1640525</t>
+          <t>1698985</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>455926</t>
+          <t>457727</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>512881</t>
+          <t>513229</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>451877</t>
+          <t>453138</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>494257</t>
+          <t>493058</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>927135</t>
+          <t>927677</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>993691</t>
+          <t>992982</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,83%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125423</t>
+          <t>125075</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>182378</t>
+          <t>180577</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159959</t>
+          <t>161158</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>202339</t>
+          <t>201078</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>298828</t>
+          <t>299537</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>365384</t>
+          <t>364842</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2492358</t>
+          <t>2497232</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2777745</t>
+          <t>2742721</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1895744</t>
+          <t>1837181</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2509408</t>
+          <t>2499740</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4435516</t>
+          <t>4436756</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5119581</t>
+          <t>5134466</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,41%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>571206</t>
+          <t>606230</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>856593</t>
+          <t>851719</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1041512</t>
+          <t>1051180</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1655176</t>
+          <t>1713739</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1780290</t>
+          <t>1765405</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2464355</t>
+          <t>2463115</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_1_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>715849</t>
+          <t>715556</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>770460</t>
+          <t>772268</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>821955</t>
+          <t>826731</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>888029</t>
+          <t>894086</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1558857</t>
+          <t>1555180</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1648372</t>
+          <t>1649059</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>248868</t>
+          <t>247060</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>303479</t>
+          <t>303772</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>420360</t>
+          <t>414303</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>486434</t>
+          <t>481658</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>679345</t>
+          <t>678658</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>768860</t>
+          <t>772537</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1402471</t>
+          <t>1398735</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1460850</t>
+          <t>1456744</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1260626</t>
+          <t>1263287</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1320486</t>
+          <t>1322950</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2680751</t>
+          <t>2680425</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2764951</t>
+          <t>2766418</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>204493</t>
+          <t>208599</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>262872</t>
+          <t>266608</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>252787</t>
+          <t>250323</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>312647</t>
+          <t>309986</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>473666</t>
+          <t>472199</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>557866</t>
+          <t>558192</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>436200</t>
+          <t>436085</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>472008</t>
+          <t>472536</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>379505</t>
+          <t>379468</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>411829</t>
+          <t>410916</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>828307</t>
+          <t>823938</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>873958</t>
+          <t>875640</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72926</t>
+          <t>72398</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108734</t>
+          <t>108849</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63647</t>
+          <t>64560</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95971</t>
+          <t>96008</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146451</t>
+          <t>144769</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192102</t>
+          <t>196471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2582930</t>
+          <t>2579842</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2674378</t>
+          <t>2675558</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2498276</t>
+          <t>2496057</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2596209</t>
+          <t>2595772</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5112156</t>
+          <t>5117800</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5243770</t>
+          <t>5248057</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>555227</t>
+          <t>554047</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>646675</t>
+          <t>649763</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>760929</t>
+          <t>761366</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>858862</t>
+          <t>861081</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1342973</t>
+          <t>1338686</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1474587</t>
+          <t>1468943</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>598836</t>
+          <t>601460</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>663580</t>
+          <t>663947</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>720591</t>
+          <t>714857</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>793971</t>
+          <t>792522</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1342535</t>
+          <t>1339992</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1434820</t>
+          <t>1439009</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,46%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>305610</t>
+          <t>305243</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>370354</t>
+          <t>367730</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>540738</t>
+          <t>542187</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>614118</t>
+          <t>619852</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>869079</t>
+          <t>864890</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>961364</t>
+          <t>963907</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1481020</t>
+          <t>1478869</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1555293</t>
+          <t>1556699</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1225393</t>
+          <t>1226502</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1302014</t>
+          <t>1300938</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2725328</t>
+          <t>2725417</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2842446</t>
+          <t>2841073</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,63%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>400898</t>
+          <t>399492</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>475171</t>
+          <t>477322</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>449525</t>
+          <t>450601</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>526146</t>
+          <t>525037</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>865284</t>
+          <t>866657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>982402</t>
+          <t>982313</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>350139</t>
+          <t>351732</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>389777</t>
+          <t>391761</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>353969</t>
+          <t>353359</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>390212</t>
+          <t>388054</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>719092</t>
+          <t>715528</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>770383</t>
+          <t>769090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,83%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91404</t>
+          <t>89420</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131042</t>
+          <t>129449</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68419</t>
+          <t>70577</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>104662</t>
+          <t>105272</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>169430</t>
+          <t>170723</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>220721</t>
+          <t>224285</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2474890</t>
+          <t>2468881</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2581412</t>
+          <t>2572878</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2333200</t>
+          <t>2331898</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2445622</t>
+          <t>2449052</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4835130</t>
+          <t>4830865</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5000791</t>
+          <t>4986472</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>825151</t>
+          <t>833685</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931673</t>
+          <t>937682</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1099257</t>
+          <t>1095827</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1211679</t>
+          <t>1212981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1950651</t>
+          <t>1964970</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2116312</t>
+          <t>2120577</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,51%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>503990</t>
+          <t>503832</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>552436</t>
+          <t>553954</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>560160</t>
+          <t>556431</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>625834</t>
+          <t>622795</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1078417</t>
+          <t>1078776</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1157105</t>
+          <t>1160980</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,78%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199904</t>
+          <t>198386</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>248350</t>
+          <t>248508</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>360273</t>
+          <t>363312</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>425947</t>
+          <t>429676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>581342</t>
+          <t>577467</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>660030</t>
+          <t>659671</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1583051</t>
+          <t>1585382</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1658541</t>
+          <t>1664064</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1450476</t>
+          <t>1443547</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1526268</t>
+          <t>1526597</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3052811</t>
+          <t>3060000</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3168567</t>
+          <t>3169002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413084</t>
+          <t>407561</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>488574</t>
+          <t>486243</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>456045</t>
+          <t>455716</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>531837</t>
+          <t>538766</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>885371</t>
+          <t>884936</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1001127</t>
+          <t>993938</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>412760</t>
+          <t>411832</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>453189</t>
+          <t>452763</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>411655</t>
+          <t>410840</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>450312</t>
+          <t>450403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>836189</t>
+          <t>836075</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>888312</t>
+          <t>892491</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,43%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93697</t>
+          <t>94123</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134126</t>
+          <t>135054</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98828</t>
+          <t>98737</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137485</t>
+          <t>138300</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>207715</t>
+          <t>203536</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>259838</t>
+          <t>259952</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2535032</t>
+          <t>2542270</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2633441</t>
+          <t>2637158</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2457747</t>
+          <t>2461367</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2573138</t>
+          <t>2568423</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5023181</t>
+          <t>5033731</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5177445</t>
+          <t>5171633</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>737411</t>
+          <t>733694</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>835820</t>
+          <t>828582</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>944423</t>
+          <t>949138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1059814</t>
+          <t>1056194</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1710968</t>
+          <t>1716780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1865232</t>
+          <t>1854682</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>332348</t>
+          <t>379775</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>313265</t>
+          <t>359255</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>350918</t>
+          <t>399716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>431794</t>
+          <t>473227</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>411879</t>
+          <t>451085</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>450684</t>
+          <t>494334</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>764142</t>
+          <t>853001</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>818959</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>792333</t>
+          <t>883355</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,57%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>167398</t>
+          <t>181474</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>148828</t>
+          <t>161533</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>186481</t>
+          <t>201994</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>289193</t>
+          <t>312774</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270303</t>
+          <t>291667</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>309108</t>
+          <t>334916</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>456592</t>
+          <t>494249</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>428401</t>
+          <t>463895</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>482781</t>
+          <t>528291</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,21%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>499746</t>
+          <t>561249</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>499746</t>
+          <t>561249</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>499746</t>
+          <t>561249</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>720987</t>
+          <t>786001</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>720987</t>
+          <t>786001</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>720987</t>
+          <t>786001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1220734</t>
+          <t>1347250</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1220734</t>
+          <t>1347250</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1220734</t>
+          <t>1347250</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1754258</t>
+          <t>1653422</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1679512</t>
+          <t>1610353</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1925836</t>
+          <t>1691870</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1435570</t>
+          <t>1505228</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1054759</t>
+          <t>1468393</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1612874</t>
+          <t>1542559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3189827</t>
+          <t>3158650</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2687633</t>
+          <t>3101957</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3398512</t>
+          <t>3217435</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>75,58%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>456643</t>
+          <t>500185</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>285065</t>
+          <t>461737</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>531389</t>
+          <t>543254</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>740148</t>
+          <t>598248</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>562844</t>
+          <t>560917</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1120959</t>
+          <t>635083</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1196791</t>
+          <t>1098434</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>988106</t>
+          <t>1039649</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1698985</t>
+          <t>1155127</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2210901</t>
+          <t>2153607</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2210901</t>
+          <t>2153607</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2210901</t>
+          <t>2153607</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2175718</t>
+          <t>2103476</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2175718</t>
+          <t>2103476</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2175718</t>
+          <t>2103476</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4386618</t>
+          <t>4257084</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4386618</t>
+          <t>4257084</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4386618</t>
+          <t>4257084</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>488381</t>
+          <t>544408</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>457727</t>
+          <t>518901</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>513229</t>
+          <t>567421</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>473788</t>
+          <t>527390</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>453138</t>
+          <t>504529</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>493058</t>
+          <t>548298</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>962168</t>
+          <t>1071798</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>927677</t>
+          <t>1038073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>992982</t>
+          <t>1104979</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>77,29%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>149923</t>
+          <t>157141</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125075</t>
+          <t>134128</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180577</t>
+          <t>182648</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>180428</t>
+          <t>200659</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>161158</t>
+          <t>179751</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>201078</t>
+          <t>223520</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>330351</t>
+          <t>357800</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>299537</t>
+          <t>324619</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>364842</t>
+          <t>391525</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>638304</t>
+          <t>701549</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>638304</t>
+          <t>701549</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>638304</t>
+          <t>701549</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>654216</t>
+          <t>728049</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>654216</t>
+          <t>728049</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>654216</t>
+          <t>728049</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1292519</t>
+          <t>1429598</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1292519</t>
+          <t>1429598</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1292519</t>
+          <t>1429598</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2574986</t>
+          <t>2577605</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2497232</t>
+          <t>2524866</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2742721</t>
+          <t>2632976</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2341151</t>
+          <t>2505844</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1837181</t>
+          <t>2460917</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2499740</t>
+          <t>2557318</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4916137</t>
+          <t>5083449</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4436756</t>
+          <t>5017040</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5134466</t>
+          <t>5156933</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>73,32%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>773965</t>
+          <t>838801</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>606230</t>
+          <t>783430</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>851719</t>
+          <t>891540</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1209769</t>
+          <t>1111682</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1051180</t>
+          <t>1060208</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1713739</t>
+          <t>1156609</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1983734</t>
+          <t>1950483</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1765405</t>
+          <t>1876999</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2463115</t>
+          <t>2016892</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3348951</t>
+          <t>3416406</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3348951</t>
+          <t>3416406</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3348951</t>
+          <t>3416406</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3550920</t>
+          <t>3617526</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3550920</t>
+          <t>3617526</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3550920</t>
+          <t>3617526</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6899871</t>
+          <t>7033932</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6899871</t>
+          <t>7033932</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6899871</t>
+          <t>7033932</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
